--- a/doc/lang/zh-Hans_fix.xlsx
+++ b/doc/lang/zh-Hans_fix.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="585" windowWidth="27735" windowHeight="11700"/>
+    <workbookView xWindow="516" yWindow="588" windowWidth="27732" windowHeight="11700"/>
   </bookViews>
   <sheets>
     <sheet name="zh-Hans" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>key</t>
   </si>
@@ -29,6 +29,26 @@
   </si>
   <si>
     <t>zh-Hans</t>
+  </si>
+  <si>
+    <t>garden.tip1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#00ff00&gt;%s&lt;/color&gt;&lt;color=#ffffff&gt;可收获&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>garden.tip2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#ffffff&gt;剩余&lt;/color&gt;&lt;color=#3aff3a&gt;%s次&lt;/color&gt;&lt;color=#ffffff&gt;收获&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#ffffff&gt;剩余&lt;/color&gt;&lt;color=#3aff3a&gt;%s次&lt;/color&gt;&lt;color=#ffffff&gt;收获&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -419,13 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11.875" customWidth="1"/>
+    <col min="1" max="3" width="11.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,7 +456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -445,6 +465,28 @@
       </c>
       <c r="C2" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
